--- a/mapping/PDTD_DTM/Mapping_FCT_RLOS_LOAN_DISBURSEMENT.xlsx
+++ b/mapping/PDTD_DTM/Mapping_FCT_RLOS_LOAN_DISBURSEMENT.xlsx
@@ -706,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Fact giải ngân khoản vay T24 (grain hợp đồng), bổ sung liên kết hồ sơ RLOS qua SEAB_LOS_ID, vùng kinh doanh, nhóm nợ</t>
+          <t>Bảng FACT đối chiếu T24, lưu khoản vay đã giải ngân của hệ RLOS, nối ngược về hồ sơ LOS qua SEAB_LOS_ID</t>
         </is>
       </c>
       <c r="E2" s="52" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B3" s="19" t="inlineStr">
         <is>
-          <t>DAYID + CONTRACT</t>
+          <t>DAYID + T24_CONTRACT</t>
         </is>
       </c>
       <c r="E3" s="52" t="inlineStr">
@@ -895,57 +895,57 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>T24_CUSTOMER_SK</t>
         </is>
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Mã hợp đồng khoản vay</t>
+          <t>Khóa khách hàng T24</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
         <is>
-          <t>PK (2/2) — mã hợp đồng khoản vay</t>
+          <t>ĐỔI TÊN từ CUSTOMER_SK (rõ nghĩa chân khách hàng T24) — khóa tới DIM_T24_CUSTOMER</t>
         </is>
       </c>
       <c r="E18" s="31" t="inlineStr">
         <is>
-          <t>A.CONTRACT</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
+          <t>A.CUSTOMER_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
         <is>
-          <t>CUSTOMER_SK</t>
+          <t>T24_CUSTOMER_CODE</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(50)</t>
         </is>
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới khách hàng T24</t>
+          <t>Mã khách hàng T24</t>
         </is>
       </c>
       <c r="D19" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_T24_CUSTOMER</t>
+          <t>CỘT MỚI — BK cạnh SK, mã khách hàng T24, giá trị đã có sẵn trong bước lookup T24_CUSTOMER_SK</t>
         </is>
       </c>
       <c r="E19" s="31" t="inlineStr">
         <is>
-          <t>A.CUSTOMER_SK</t>
+          <t>A.CUSTOMER_CODE</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới đơn vị kinh doanh T24</t>
+          <t>Khóa đơn vị kinh doanh T24</t>
         </is>
       </c>
       <c r="D20" s="54" t="inlineStr">
@@ -976,271 +976,352 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>CONTRACT_SK</t>
+          <t>T24_COMPANY_CODE</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
+          <t>VARCHAR2(50)</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Mã đơn vị kinh doanh T24</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK, mã công ty/chi nhánh T24, giá trị đã có sẵn trong bước lookup T24_COMPANY_SK</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>A.CO_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>T24_CONTRACT_SK</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới hợp đồng T24</t>
-        </is>
-      </c>
-      <c r="D21" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_T24_LOAN</t>
-        </is>
-      </c>
-      <c r="E21" s="31" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Khóa hợp đồng T24</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>ĐỔI TÊN từ CONTRACT_SK (rõ nghĩa chân T24) — khóa tới DIM_T24_LOAN</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>A.CONTRACT_SK</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>SEAB_PRODUCTS_DE_SK</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>T24_CONTRACT</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Mã hợp đồng khoản vay</t>
+        </is>
+      </c>
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>PK (2/2) — ĐỔI TÊN từ CONTRACT, chuyển vị trí xuống ngay sau T24_CONTRACT_SK để đồng bộ nhóm BK cạnh SK — mã hợp đồng khoản vay</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>A.CONTRACT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>T24_SEAB_PRODUCTS_DE_SK</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới sản phẩm T24</t>
-        </is>
-      </c>
-      <c r="D22" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_T24_SEAB_PRODUCTS_DE</t>
-        </is>
-      </c>
-      <c r="E22" s="31" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Khóa sản phẩm T24</t>
+        </is>
+      </c>
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>ĐỔI TÊN từ SEAB_PRODUCTS_DE_SK (rõ nghĩa chân T24) — khóa tới DIM_T24_SEAB_PRODUCTS_DE</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
         <is>
           <t>A.SEAB_PRODUCTS_DE_SK</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>APPLICATION_SK</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới hồ sơ tín dụng</t>
-        </is>
-      </c>
-      <c r="D23" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_RLOS_APPLICATION, tra theo SEAB_LOS_ID</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN C ON C.WI_NAME = A.SEAB_LOS_ID → C.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>SEAB_LOS_ID</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>T24_SEAB_PRODUCTS_DE</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ LOS</t>
-        </is>
-      </c>
-      <c r="D24" s="54" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ LOS do T24 lưu, gắn với hợp đồng</t>
-        </is>
-      </c>
-      <c r="E24" s="31" t="inlineStr">
-        <is>
-          <t>A.SEAB_LOS_ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>ZONE</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(50)</t>
-        </is>
-      </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Vùng kinh doanh</t>
+          <t>Mã sản phẩm T24</t>
         </is>
       </c>
       <c r="D25" s="54" t="inlineStr">
         <is>
-          <t>Tên vùng của đơn vị kinh doanh</t>
+          <t>CỘT MỚI — BK cạnh SK, giá trị đã có sẵn trong bước lookup T24_SEAB_PRODUCTS_DE_SK</t>
         </is>
       </c>
       <c r="E25" s="31" t="inlineStr">
         <is>
-          <t>LEFT JOIN D ON D.COMPANY_CODE = A.CO_CODE → D.ZONE</t>
+          <t>A.SEAB_PRODUCTS_DE</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>DISBURSEMENT_AMT</t>
+          <t>APPLICATION_SK</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>NUMBER(20,2)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Số tiền giải ngân</t>
+          <t>Khóa hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D26" s="54" t="inlineStr">
         <is>
-          <t>Số tiền giải ngân</t>
+          <t>Khóa tới DIM_RLOS_APPLICATION, tra theo SEAB_LOS_ID</t>
         </is>
       </c>
       <c r="E26" s="31" t="inlineStr">
         <is>
-          <t>ABS(A.FIRST_DISBURSEMENT_AMT)</t>
+          <t>LEFT JOIN C ON C.WI_NAME = A.SEAB_LOS_ID → C.DIMENSION_KEY</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>CUR_BALANCE</t>
+          <t>SEAB_LOS_ID</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>NUMBER(20,2)</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Dư nợ hiện tại</t>
+          <t>Mã hồ sơ LOS</t>
         </is>
       </c>
       <c r="D27" s="54" t="inlineStr">
         <is>
-          <t>Dư nợ hiện tại</t>
+          <t>Mã hồ sơ LOS do T24 lưu, gắn với hợp đồng</t>
         </is>
       </c>
       <c r="E27" s="31" t="inlineStr">
         <is>
-          <t>(ABS(NVL(A.BALANCE,0)) + ABS(NVL(A.PD_BALANCE,0))) * A.REVAL_RATE</t>
+          <t>A.SEAB_LOS_ID</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
+          <t>ZONE</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(50)</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Vùng kinh doanh</t>
+        </is>
+      </c>
+      <c r="D28" s="54" t="inlineStr">
+        <is>
+          <t>Tên vùng của đơn vị kinh doanh</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>LEFT JOIN D ON D.COMPANY_CODE = A.CO_CODE → D.ZONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>DISBURSEMENT_AMT</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER(20,2)</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Số tiền giải ngân</t>
+        </is>
+      </c>
+      <c r="D29" s="54" t="inlineStr">
+        <is>
+          <t>Số tiền giải ngân</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>ABS(A.FIRST_DISBURSEMENT_AMT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>CUR_BALANCE</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER(20,2)</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Dư nợ hiện tại</t>
+        </is>
+      </c>
+      <c r="D30" s="54" t="inlineStr">
+        <is>
+          <t>Dư nợ hiện tại</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
+        <is>
+          <t>(ABS(NVL(A.BALANCE,0)) + ABS(NVL(A.PD_BALANCE,0))) * A.REVAL_RATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
           <t>NO_DAYS_OVERDUE</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>NUMBER(6)</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>Số ngày quá hạn</t>
         </is>
       </c>
-      <c r="D28" s="54" t="inlineStr">
+      <c r="D31" s="54" t="inlineStr">
         <is>
           <t>Số ngày quá hạn — self-join chính bảng driving qua PD_CONTRACT</t>
         </is>
       </c>
-      <c r="E28" s="31" t="inlineStr">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>LEFT JOIN E2 ON E2.CONTRACT = A.PD_CONTRACT → E2.NO_DAYS_OVERDUE</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>CUR_BUCKET</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>NUMBER(2)</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
         <is>
           <t>Nhóm nợ</t>
         </is>
       </c>
-      <c r="D29" s="54" t="inlineStr">
+      <c r="D32" s="54" t="inlineStr">
         <is>
           <t>Nhóm nợ — cùng self-join PD_CONTRACT như NO_DAYS_OVERDUE, dùng chung alias E2</t>
         </is>
       </c>
-      <c r="E29" s="31" t="inlineStr">
+      <c r="E32" s="31" t="inlineStr">
         <is>
           <t>LEFT JOIN E2 ON E2.CONTRACT = A.PD_CONTRACT → CASE WHEN E2.NO_DAYS_OVERDUE &gt; 360 THEN 5 WHEN E2.NO_DAYS_OVERDUE &gt; 180 THEN 4 WHEN E2.NO_DAYS_OVERDUE &gt; 90 THEN 3 WHEN E2.NO_DAYS_OVERDUE &gt;= 10 THEN 2 ELSE 1 END</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>APPROVAL_DATE</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>Ngày phê duyệt</t>
         </is>
       </c>
-      <c r="D30" s="54" t="inlineStr">
+      <c r="D33" s="54" t="inlineStr">
         <is>
           <t>Ngày phê duyệt — denormalize qua APPLICATION_SK đã có sẵn trên fact, không JOIN fact-to-fact</t>
         </is>
       </c>
-      <c r="E30" s="31" t="inlineStr">
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>C.LAST_APPROVAL_DATE</t>
         </is>
